--- a/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/1.项目背景.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/1.项目背景.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,10 +451,64 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>背景A</t>
+          <t>客户计划 Q3 上线 384 节点训练集群，替代现有 GPU 租赁方案，要求算力自主可控与液冷节能。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>goal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>客户项目目标</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>建设 384 节点昇腾训练集群，支持大模型训练与推理业务，实现算力自主可控。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>客户项目范围</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>算力底座（Atlas 900 A3 SuperPoD）+ 网络（400G RoCE）+ 存储（OceanStor）+ 液冷系统，含机房改造与上电。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>客户项目计划</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>客户里程碑：2026-06-01 机房就绪 → 2026-07-20 到货 → 2026-08-10 上线；与第 12 章计划联动</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
